--- a/mapping/mapping1.xlsx
+++ b/mapping/mapping1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\Practice\Python codes\Mappings\Episode 2\data\mapping\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\d\OneDrive - Indian Institute of Foreign Trade\Desktop\Practice\Python codes\Mappings\Python to Python\gen14\data\mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BFAB42C-5C2E-49D5-8297-69F47C1B7908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1901D536-7B4F-4168-BE59-4A894846AC78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4020" yWindow="4020" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="24">
   <si>
     <t>a1</t>
   </si>
@@ -56,9 +56,6 @@
     <t>a5</t>
   </si>
   <si>
-    <t>id_01</t>
-  </si>
-  <si>
     <t>id_02</t>
   </si>
   <si>
@@ -74,9 +71,6 @@
     <t>a5_04</t>
   </si>
   <si>
-    <t>ida_01</t>
-  </si>
-  <si>
     <t>ida_02</t>
   </si>
   <si>
@@ -84,13 +78,55 @@
   </si>
   <si>
     <t>a2</t>
+  </si>
+  <si>
+    <t>a6</t>
+  </si>
+  <si>
+    <t>a6_01</t>
+  </si>
+  <si>
+    <t>a6_02</t>
+  </si>
+  <si>
+    <t>a6_04</t>
+  </si>
+  <si>
+    <t>a7</t>
+  </si>
+  <si>
+    <t>a8</t>
+  </si>
+  <si>
+    <t>a9</t>
+  </si>
+  <si>
+    <t>a10</t>
+  </si>
+  <si>
+    <t>a11</t>
+  </si>
+  <si>
+    <t>a12</t>
+  </si>
+  <si>
+    <t>a13</t>
+  </si>
+  <si>
+    <t>a14</t>
+  </si>
+  <si>
+    <t>a15</t>
+  </si>
+  <si>
+    <t>idabc_02</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,6 +142,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -115,7 +157,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -138,15 +180,29 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -451,54 +507,175 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M4" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>